--- a/backend/data/financials_by_company/1CEC.MI.xlsx
+++ b/backend/data/financials_by_company/1CEC.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,547 +669,483 @@
           <t>Operating Revenue</t>
         </is>
       </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Rent Expense Supplemental</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Rent And Landing Fees</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Cost Of Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45565</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-640000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1002000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-5000000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-5000000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>76000000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>662000000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>18481000000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>997000000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>335000000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-186000000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>247000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>70000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>80360000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>76000000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>22213000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>513080862</v>
-      </c>
-      <c r="S2" t="n">
-        <v>485221084</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V2" t="n">
-        <v>84000000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>76000000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>76000000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>77000000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>77000000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>88000000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-4000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-6000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>10000000</v>
-      </c>
+        <v>44469</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>-186000000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>247000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>70000000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>229000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>3732000000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>2139000000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1808000000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>331000000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3961000000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>22442000000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>22442000000</v>
-      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45199</v>
+        <v>44834</v>
       </c>
       <c r="B3" t="n">
-        <v>-7620000</v>
+        <v>300000</v>
       </c>
       <c r="C3" t="n">
-        <v>0.127</v>
+        <v>0.15</v>
       </c>
       <c r="D3" t="n">
-        <v>1018000000</v>
+        <v>879000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-60000000</v>
+        <v>2000000</v>
       </c>
       <c r="F3" t="n">
-        <v>-60000000</v>
+        <v>2000000</v>
       </c>
       <c r="G3" t="n">
-        <v>-39000000</v>
+        <v>126000000</v>
       </c>
       <c r="H3" t="n">
-        <v>835000000</v>
+        <v>761000000</v>
       </c>
       <c r="I3" t="n">
-        <v>18303000000</v>
+        <v>17961000000</v>
       </c>
       <c r="J3" t="n">
-        <v>958000000</v>
+        <v>881000000</v>
       </c>
       <c r="K3" t="n">
-        <v>123000000</v>
+        <v>120000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-34000000</v>
+        <v>-44000000</v>
       </c>
       <c r="M3" t="n">
-        <v>165000000</v>
+        <v>71000000</v>
       </c>
       <c r="N3" t="n">
-        <v>64000000</v>
+        <v>24000000</v>
       </c>
       <c r="O3" t="n">
-        <v>13380000</v>
+        <v>124300000</v>
       </c>
       <c r="P3" t="n">
-        <v>-39000000</v>
+        <v>126000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>22080000000</v>
+        <v>21642000000</v>
       </c>
       <c r="R3" t="n">
-        <v>513080862</v>
+        <v>409481398</v>
       </c>
       <c r="S3" t="n">
-        <v>485221084</v>
+        <v>400779988</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.08</v>
+        <v>0.31</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.08</v>
+        <v>0.31</v>
       </c>
       <c r="V3" t="n">
-        <v>-31000000</v>
+        <v>128000000</v>
       </c>
       <c r="W3" t="n">
-        <v>7000000</v>
+        <v>2000000</v>
       </c>
       <c r="X3" t="n">
-        <v>-39000000</v>
+        <v>126000000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-39000000</v>
+        <v>126000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2000000</v>
+        <v>-4000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-37000000</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>130000000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
       <c r="AD3" t="n">
-        <v>-37000000</v>
+        <v>130000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-5000000</v>
+        <v>-81000000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-42000000</v>
+        <v>49000000</v>
       </c>
       <c r="AG3" t="n">
-        <v>7000000</v>
+        <v>8000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-59000000</v>
+        <v>-1000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>43000000</v>
+        <v>-4000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16000000</v>
+        <v>5000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>69000000</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-34000000</v>
+        <v>-44000000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-67000000</v>
+        <v>-3000000</v>
       </c>
       <c r="AN3" t="n">
-        <v>165000000</v>
+        <v>71000000</v>
       </c>
       <c r="AO3" t="n">
-        <v>64000000</v>
+        <v>24000000</v>
       </c>
       <c r="AP3" t="n">
-        <v>162000000</v>
+        <v>126000000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3777000000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>69000000</v>
-      </c>
+        <v>3681000000</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>2117000000</v>
+        <v>2098000000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1804000000</v>
+        <v>1768000000</v>
       </c>
       <c r="AU3" t="n">
-        <v>313000000</v>
+        <v>330000000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3939000000</v>
+        <v>3807000000</v>
       </c>
       <c r="AW3" t="n">
-        <v>22242000000</v>
+        <v>21768000000</v>
       </c>
       <c r="AX3" t="n">
-        <v>22242000000</v>
-      </c>
+        <v>21768000000</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44834</v>
+        <v>45199</v>
       </c>
       <c r="B4" t="n">
-        <v>300000</v>
+        <v>-7620000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.15</v>
+        <v>0.127</v>
       </c>
       <c r="D4" t="n">
-        <v>879000000</v>
+        <v>1018000000</v>
       </c>
       <c r="E4" t="n">
-        <v>2000000</v>
+        <v>-60000000</v>
       </c>
       <c r="F4" t="n">
-        <v>2000000</v>
+        <v>-60000000</v>
       </c>
       <c r="G4" t="n">
-        <v>126000000</v>
+        <v>-39000000</v>
       </c>
       <c r="H4" t="n">
-        <v>761000000</v>
+        <v>835000000</v>
       </c>
       <c r="I4" t="n">
-        <v>17961000000</v>
+        <v>18303000000</v>
       </c>
       <c r="J4" t="n">
-        <v>881000000</v>
+        <v>958000000</v>
       </c>
       <c r="K4" t="n">
-        <v>120000000</v>
+        <v>123000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-44000000</v>
+        <v>-34000000</v>
       </c>
       <c r="M4" t="n">
-        <v>71000000</v>
+        <v>165000000</v>
       </c>
       <c r="N4" t="n">
-        <v>24000000</v>
+        <v>64000000</v>
       </c>
       <c r="O4" t="n">
-        <v>124300000</v>
+        <v>13380000</v>
       </c>
       <c r="P4" t="n">
-        <v>126000000</v>
+        <v>-39000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>21642000000</v>
+        <v>22080000000</v>
       </c>
       <c r="R4" t="n">
-        <v>409481398</v>
+        <v>513080862</v>
       </c>
       <c r="S4" t="n">
-        <v>400779988</v>
+        <v>485221084</v>
       </c>
       <c r="T4" t="n">
-        <v>0.31</v>
+        <v>-0.08</v>
       </c>
       <c r="U4" t="n">
-        <v>0.31</v>
+        <v>-0.08</v>
       </c>
       <c r="V4" t="n">
-        <v>128000000</v>
+        <v>-31000000</v>
       </c>
       <c r="W4" t="n">
-        <v>2000000</v>
+        <v>7000000</v>
       </c>
       <c r="X4" t="n">
-        <v>126000000</v>
+        <v>-39000000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>126000000</v>
+        <v>-39000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-4000000</v>
+        <v>-2000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
+        <v>-37000000</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>130000000</v>
+        <v>-37000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-81000000</v>
+        <v>-5000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>49000000</v>
+        <v>-42000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>8000000</v>
+        <v>7000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1000000</v>
+        <v>-59000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-4000000</v>
+        <v>43000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5000000</v>
+        <v>16000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>69000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-44000000</v>
+        <v>-34000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-3000000</v>
+        <v>-67000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>71000000</v>
+        <v>165000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>24000000</v>
+        <v>64000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>126000000</v>
+        <v>162000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3681000000</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+        <v>3777000000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>69000000</v>
+      </c>
       <c r="AS4" t="n">
-        <v>2098000000</v>
+        <v>2117000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1768000000</v>
+        <v>1804000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>330000000</v>
+        <v>313000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3807000000</v>
+        <v>3939000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>21768000000</v>
+        <v>22242000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>21768000000</v>
-      </c>
+        <v>22242000000</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44469</v>
+        <v>45565</v>
       </c>
       <c r="B5" t="n">
-        <v>-2492000</v>
+        <v>-625000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.178</v>
+        <v>0.125</v>
       </c>
       <c r="D5" t="n">
-        <v>998000000</v>
+        <v>1002000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-14000000</v>
+        <v>-5000000</v>
       </c>
       <c r="F5" t="n">
-        <v>-14000000</v>
+        <v>-5000000</v>
       </c>
       <c r="G5" t="n">
-        <v>219000000</v>
+        <v>76000000</v>
       </c>
       <c r="H5" t="n">
-        <v>621000000</v>
+        <v>662000000</v>
       </c>
       <c r="I5" t="n">
-        <v>17705000000</v>
+        <v>18481000000</v>
       </c>
       <c r="J5" t="n">
-        <v>984000000</v>
+        <v>997000000</v>
       </c>
       <c r="K5" t="n">
-        <v>363000000</v>
+        <v>335000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-71000000</v>
+        <v>-186000000</v>
       </c>
       <c r="M5" t="n">
-        <v>67000000</v>
+        <v>247000000</v>
       </c>
       <c r="N5" t="n">
-        <v>14000000</v>
+        <v>70000000</v>
       </c>
       <c r="O5" t="n">
-        <v>230508000</v>
+        <v>80375000</v>
       </c>
       <c r="P5" t="n">
-        <v>232000000</v>
+        <v>76000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>21193000000</v>
+        <v>22213000000</v>
       </c>
       <c r="R5" t="n">
-        <v>359421084</v>
+        <v>513080862</v>
       </c>
       <c r="S5" t="n">
-        <v>359421084</v>
+        <v>485221084</v>
       </c>
       <c r="T5" t="n">
-        <v>0.65</v>
+        <v>0.16</v>
       </c>
       <c r="U5" t="n">
-        <v>0.65</v>
+        <v>0.16</v>
       </c>
       <c r="V5" t="n">
-        <v>232000000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>84000000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>8000000</v>
+      </c>
       <c r="X5" t="n">
-        <v>232000000</v>
+        <v>76000000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>232000000</v>
+        <v>76000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-24000000</v>
+        <v>-1000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>256000000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>13000000</v>
-      </c>
+        <v>77000000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>243000000</v>
+        <v>77000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>53000000</v>
+        <v>11000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>296000000</v>
+        <v>88000000</v>
       </c>
       <c r="AG5" t="n">
         <v>7000000</v>
@@ -1218,50 +1154,210 @@
         <v>-4000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1000000</v>
+        <v>-6000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-71000000</v>
+        <v>-186000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>18000000</v>
+        <v>9000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>67000000</v>
+        <v>247000000</v>
       </c>
       <c r="AO5" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>229000000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3732000000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>2139000000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1808000000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>331000000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3961000000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>22442000000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>22442000000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>995000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-25000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-35000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>701000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>18918000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>970000000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>269000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-196000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>241000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="O6" t="n">
         <v>14000000</v>
       </c>
-      <c r="AP5" t="n">
-        <v>168000000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3488000000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1988000000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1703000000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>285000000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3656000000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>21361000000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>21361000000</v>
+      <c r="P6" t="n">
+        <v>-35000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>22796000000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>513080862</v>
+      </c>
+      <c r="S6" t="n">
+        <v>485221084</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-26000000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-35000000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-35000000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-34000000</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>-34000000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>-196000000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>241000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>276000000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3878000000</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>2207000000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1835000000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>372000000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4154000000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>23072000000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>23072000000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>18918000000</v>
       </c>
     </row>
   </sheetData>
@@ -1275,7 +1371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU5"/>
+  <dimension ref="A1:BU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1642,224 +1738,90 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45565</v>
-      </c>
-      <c r="B2" t="n">
-        <v>485221084</v>
-      </c>
-      <c r="C2" t="n">
-        <v>485221084</v>
-      </c>
+        <v>44469</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>2631000000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-193000000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1422000000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-617000000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-193000000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1725000000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>516000000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1354000000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>515000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>516000000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-1113000000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>389000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1240000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1240000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>9620000000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2548000000</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>328000000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2096000000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1258000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>838000000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>88000000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>7072000000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>81000000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>535000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>467000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>68000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>134000000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>5744000000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>235000000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>5509000000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>10135000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>3680000000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>356000000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>67000000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>67000000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>275000000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>709000000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>185000000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>524000000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2218000000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-2282000000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4500000000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="BC2" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="n">
         <v>3000000</v>
       </c>
-      <c r="BD2" t="n">
-        <v>2833000000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1620000000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>6455000000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>55000000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>3114000000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>-80000000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>3194000000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>339000000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>283000000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1513000000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1150000000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>140000000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1010000000</v>
-      </c>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="n">
-        <v>1010000000</v>
-      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="n">
+        <v>1531000000</v>
+      </c>
+      <c r="BU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45199</v>
+        <v>44834</v>
       </c>
       <c r="B3" t="n">
         <v>485221084</v>
@@ -1867,42 +1829,44 @@
       <c r="C3" t="n">
         <v>485221084</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>43000000</v>
+      </c>
       <c r="E3" t="n">
-        <v>2584000000</v>
+        <v>2772000000</v>
       </c>
       <c r="F3" t="n">
-        <v>-226000000</v>
+        <v>-86000000</v>
       </c>
       <c r="G3" t="n">
-        <v>1262000000</v>
+        <v>1401000000</v>
       </c>
       <c r="H3" t="n">
-        <v>-708000000</v>
+        <v>-631000000</v>
       </c>
       <c r="I3" t="n">
-        <v>-226000000</v>
+        <v>-86000000</v>
       </c>
       <c r="J3" t="n">
-        <v>1785000000</v>
+        <v>1961000000</v>
       </c>
       <c r="K3" t="n">
-        <v>463000000</v>
+        <v>590000000</v>
       </c>
       <c r="L3" t="n">
-        <v>1152000000</v>
+        <v>1320000000</v>
       </c>
       <c r="M3" t="n">
-        <v>465000000</v>
+        <v>592000000</v>
       </c>
       <c r="N3" t="n">
         <v>2000000</v>
       </c>
       <c r="O3" t="n">
-        <v>463000000</v>
+        <v>590000000</v>
       </c>
       <c r="P3" t="n">
-        <v>-1166000000</v>
+        <v>-1039000000</v>
       </c>
       <c r="Q3" t="n">
         <v>389000000</v>
@@ -1914,14 +1878,14 @@
         <v>1240000000</v>
       </c>
       <c r="T3" t="n">
-        <v>9170000000</v>
+        <v>9406000000</v>
       </c>
       <c r="U3" t="n">
-        <v>2487000000</v>
+        <v>2641000000</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>316000000</v>
+        <v>332000000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -1930,100 +1894,98 @@
         <v>3000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>69000000</v>
+        <v>65000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2000000000</v>
+        <v>2184000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1311000000</v>
+        <v>1454000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>689000000</v>
+        <v>730000000</v>
       </c>
       <c r="AD3" t="n">
-        <v>88000000</v>
+        <v>43000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>6683000000</v>
+        <v>6765000000</v>
       </c>
       <c r="AF3" t="n">
-        <v>82000000</v>
+        <v>3000000</v>
       </c>
       <c r="AG3" t="n">
-        <v>584000000</v>
+        <v>588000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>474000000</v>
+        <v>507000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>110000000</v>
+        <v>81000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>118000000</v>
+        <v>95000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>5307000000</v>
+        <v>5703000000</v>
       </c>
       <c r="AL3" t="n">
-        <v>273000000</v>
+        <v>363000000</v>
       </c>
       <c r="AM3" t="n">
-        <v>5034000000</v>
+        <v>5340000000</v>
       </c>
       <c r="AN3" t="n">
-        <v>9635000000</v>
+        <v>9998000000</v>
       </c>
       <c r="AO3" t="n">
-        <v>3660000000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3000000</v>
-      </c>
+        <v>3865000000</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="AR3" t="n">
-        <v>368000000</v>
+        <v>302000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>83000000</v>
+        <v>103000000</v>
       </c>
       <c r="AT3" t="n">
-        <v>83000000</v>
+        <v>103000000</v>
       </c>
       <c r="AU3" t="n">
-        <v>257000000</v>
+        <v>388000000</v>
       </c>
       <c r="AV3" t="n">
-        <v>689000000</v>
+        <v>676000000</v>
       </c>
       <c r="AW3" t="n">
-        <v>165000000</v>
+        <v>152000000</v>
       </c>
       <c r="AX3" t="n">
         <v>524000000</v>
       </c>
       <c r="AY3" t="n">
-        <v>2216000000</v>
+        <v>2377000000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-2247000000</v>
+        <v>-2296000000</v>
       </c>
       <c r="BA3" t="n">
-        <v>4463000000</v>
+        <v>4673000000</v>
       </c>
       <c r="BB3" t="n">
-        <v>24000000</v>
+        <v>30000000</v>
       </c>
       <c r="BC3" t="n">
-        <v>6000000</v>
+        <v>14000000</v>
       </c>
       <c r="BD3" t="n">
-        <v>2760000000</v>
+        <v>2805000000</v>
       </c>
       <c r="BE3" t="n">
-        <v>1668000000</v>
+        <v>1819000000</v>
       </c>
       <c r="BF3" t="n">
         <v>5000000</v>
@@ -2032,51 +1994,51 @@
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>5975000000</v>
+        <v>6134000000</v>
       </c>
       <c r="BI3" t="n">
-        <v>4000000</v>
+        <v>3000000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>53000000</v>
+        <v>59000000</v>
       </c>
       <c r="BK3" t="n">
-        <v>2918000000</v>
+        <v>3176000000</v>
       </c>
       <c r="BL3" t="n">
-        <v>-73000000</v>
+        <v>-154000000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2991000000</v>
+        <v>3330000000</v>
       </c>
       <c r="BN3" t="n">
-        <v>280000000</v>
+        <v>221000000</v>
       </c>
       <c r="BO3" t="n">
-        <v>283000000</v>
+        <v>250000000</v>
       </c>
       <c r="BP3" t="n">
-        <v>1417000000</v>
+        <v>1515000000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1020000000</v>
+        <v>910000000</v>
       </c>
       <c r="BR3" t="n">
-        <v>123000000</v>
+        <v>142000000</v>
       </c>
       <c r="BS3" t="n">
-        <v>897000000</v>
+        <v>768000000</v>
       </c>
       <c r="BT3" t="n">
-        <v>836000000</v>
+        <v>720000000</v>
       </c>
       <c r="BU3" t="n">
-        <v>897000000</v>
+        <v>768000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44834</v>
+        <v>45199</v>
       </c>
       <c r="B4" t="n">
         <v>485221084</v>
@@ -2084,44 +2046,42 @@
       <c r="C4" t="n">
         <v>485221084</v>
       </c>
-      <c r="D4" t="n">
-        <v>43000000</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2772000000</v>
+        <v>2584000000</v>
       </c>
       <c r="F4" t="n">
-        <v>-86000000</v>
+        <v>-226000000</v>
       </c>
       <c r="G4" t="n">
-        <v>1401000000</v>
+        <v>1262000000</v>
       </c>
       <c r="H4" t="n">
-        <v>-631000000</v>
+        <v>-708000000</v>
       </c>
       <c r="I4" t="n">
-        <v>-86000000</v>
+        <v>-226000000</v>
       </c>
       <c r="J4" t="n">
-        <v>1961000000</v>
+        <v>1785000000</v>
       </c>
       <c r="K4" t="n">
-        <v>590000000</v>
+        <v>463000000</v>
       </c>
       <c r="L4" t="n">
-        <v>1320000000</v>
+        <v>1152000000</v>
       </c>
       <c r="M4" t="n">
-        <v>592000000</v>
+        <v>465000000</v>
       </c>
       <c r="N4" t="n">
         <v>2000000</v>
       </c>
       <c r="O4" t="n">
-        <v>590000000</v>
+        <v>463000000</v>
       </c>
       <c r="P4" t="n">
-        <v>-1039000000</v>
+        <v>-1166000000</v>
       </c>
       <c r="Q4" t="n">
         <v>389000000</v>
@@ -2133,14 +2093,14 @@
         <v>1240000000</v>
       </c>
       <c r="T4" t="n">
-        <v>9406000000</v>
+        <v>9170000000</v>
       </c>
       <c r="U4" t="n">
-        <v>2641000000</v>
+        <v>2487000000</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>332000000</v>
+        <v>316000000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -2149,98 +2109,100 @@
         <v>3000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>65000000</v>
+        <v>69000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>2184000000</v>
+        <v>2000000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1454000000</v>
+        <v>1311000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>730000000</v>
+        <v>689000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>43000000</v>
+        <v>88000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>6765000000</v>
+        <v>6683000000</v>
       </c>
       <c r="AF4" t="n">
+        <v>82000000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>584000000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>474000000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>110000000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>5307000000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>273000000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5034000000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>9635000000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>3660000000</v>
+      </c>
+      <c r="AP4" t="n">
         <v>3000000</v>
       </c>
-      <c r="AG4" t="n">
-        <v>588000000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>507000000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>81000000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>95000000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>5703000000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>363000000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>5340000000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>9998000000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>3865000000</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>5000000</v>
+        <v>3000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>302000000</v>
+        <v>368000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>103000000</v>
+        <v>83000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>103000000</v>
+        <v>83000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>388000000</v>
+        <v>257000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>676000000</v>
+        <v>689000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>152000000</v>
+        <v>165000000</v>
       </c>
       <c r="AX4" t="n">
         <v>524000000</v>
       </c>
       <c r="AY4" t="n">
-        <v>2377000000</v>
+        <v>2216000000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-2296000000</v>
+        <v>-2247000000</v>
       </c>
       <c r="BA4" t="n">
-        <v>4673000000</v>
+        <v>4463000000</v>
       </c>
       <c r="BB4" t="n">
-        <v>30000000</v>
+        <v>24000000</v>
       </c>
       <c r="BC4" t="n">
-        <v>14000000</v>
+        <v>6000000</v>
       </c>
       <c r="BD4" t="n">
-        <v>2805000000</v>
+        <v>2760000000</v>
       </c>
       <c r="BE4" t="n">
-        <v>1819000000</v>
+        <v>1668000000</v>
       </c>
       <c r="BF4" t="n">
         <v>5000000</v>
@@ -2249,215 +2211,217 @@
         <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>6134000000</v>
+        <v>5975000000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>59000000</v>
+        <v>53000000</v>
       </c>
       <c r="BK4" t="n">
-        <v>3176000000</v>
+        <v>2918000000</v>
       </c>
       <c r="BL4" t="n">
-        <v>-154000000</v>
+        <v>-73000000</v>
       </c>
       <c r="BM4" t="n">
-        <v>3330000000</v>
+        <v>2991000000</v>
       </c>
       <c r="BN4" t="n">
-        <v>221000000</v>
+        <v>280000000</v>
       </c>
       <c r="BO4" t="n">
-        <v>250000000</v>
+        <v>283000000</v>
       </c>
       <c r="BP4" t="n">
-        <v>1515000000</v>
+        <v>1417000000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>910000000</v>
+        <v>1020000000</v>
       </c>
       <c r="BR4" t="n">
-        <v>142000000</v>
+        <v>123000000</v>
       </c>
       <c r="BS4" t="n">
-        <v>768000000</v>
+        <v>897000000</v>
       </c>
       <c r="BT4" t="n">
-        <v>720000000</v>
+        <v>836000000</v>
       </c>
       <c r="BU4" t="n">
-        <v>768000000</v>
+        <v>897000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44469</v>
+        <v>45565</v>
       </c>
       <c r="B5" t="n">
-        <v>359421084</v>
+        <v>485221084</v>
       </c>
       <c r="C5" t="n">
-        <v>359421084</v>
+        <v>485221084</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2867000000</v>
+        <v>2631000000</v>
       </c>
       <c r="F5" t="n">
-        <v>64000000</v>
+        <v>-193000000</v>
       </c>
       <c r="G5" t="n">
-        <v>1512000000</v>
+        <v>1422000000</v>
       </c>
       <c r="H5" t="n">
-        <v>-460000000</v>
+        <v>-617000000</v>
       </c>
       <c r="I5" t="n">
-        <v>64000000</v>
+        <v>-193000000</v>
       </c>
       <c r="J5" t="n">
-        <v>2068000000</v>
+        <v>1725000000</v>
       </c>
       <c r="K5" t="n">
-        <v>713000000</v>
+        <v>516000000</v>
       </c>
       <c r="L5" t="n">
-        <v>1270000000</v>
+        <v>1354000000</v>
       </c>
       <c r="M5" t="n">
-        <v>757000000</v>
+        <v>515000000</v>
       </c>
       <c r="N5" t="n">
-        <v>44000000</v>
+        <v>-1000000</v>
       </c>
       <c r="O5" t="n">
-        <v>713000000</v>
+        <v>516000000</v>
       </c>
       <c r="P5" t="n">
-        <v>-527000000</v>
+        <v>-1113000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>321000000</v>
+        <v>389000000</v>
       </c>
       <c r="R5" t="n">
-        <v>919000000</v>
+        <v>1240000000</v>
       </c>
       <c r="S5" t="n">
-        <v>919000000</v>
+        <v>1240000000</v>
       </c>
       <c r="T5" t="n">
-        <v>9910000000</v>
+        <v>9620000000</v>
       </c>
       <c r="U5" t="n">
-        <v>2686000000</v>
+        <v>2548000000</v>
       </c>
       <c r="V5" t="n">
-        <v>-2000000</v>
+        <v>-1000000</v>
       </c>
       <c r="W5" t="n">
-        <v>462000000</v>
+        <v>328000000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>5000000</v>
+        <v>9000000</v>
       </c>
       <c r="Z5" t="n">
-        <v>29000000</v>
+        <v>15000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>2111000000</v>
+        <v>2096000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1554000000</v>
+        <v>1258000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>557000000</v>
+        <v>838000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>38000000</v>
+        <v>88000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>7224000000</v>
+        <v>7072000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>3000000</v>
+        <v>81000000</v>
       </c>
       <c r="AG5" t="n">
-        <v>756000000</v>
+        <v>535000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>514000000</v>
+        <v>467000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>242000000</v>
+        <v>68000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>108000000</v>
+        <v>134000000</v>
       </c>
       <c r="AK5" t="n">
-        <v>5914000000</v>
+        <v>5744000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>444000000</v>
+        <v>235000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>5470000000</v>
+        <v>5509000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>10667000000</v>
+        <v>10135000000</v>
       </c>
       <c r="AO5" t="n">
-        <v>3903000000</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>3680000000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1000000</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>99000000</v>
+        <v>356000000</v>
       </c>
       <c r="AS5" t="n">
-        <v>269000000</v>
+        <v>67000000</v>
       </c>
       <c r="AT5" t="n">
-        <v>269000000</v>
+        <v>67000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>425000000</v>
+        <v>275000000</v>
       </c>
       <c r="AV5" t="n">
-        <v>649000000</v>
+        <v>709000000</v>
       </c>
       <c r="AW5" t="n">
-        <v>125000000</v>
+        <v>185000000</v>
       </c>
       <c r="AX5" t="n">
         <v>524000000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2440000000</v>
+        <v>2218000000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-2263000000</v>
+        <v>-2282000000</v>
       </c>
       <c r="BA5" t="n">
-        <v>4703000000</v>
+        <v>4500000000</v>
       </c>
       <c r="BB5" t="n">
-        <v>23000000</v>
+        <v>39000000</v>
       </c>
       <c r="BC5" t="n">
-        <v>21000000</v>
+        <v>3000000</v>
       </c>
       <c r="BD5" t="n">
-        <v>2747000000</v>
+        <v>2833000000</v>
       </c>
       <c r="BE5" t="n">
-        <v>1907000000</v>
+        <v>1620000000</v>
       </c>
       <c r="BF5" t="n">
         <v>5000000</v>
@@ -2466,46 +2430,257 @@
         <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>6764000000</v>
+        <v>6455000000</v>
       </c>
       <c r="BI5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3114000000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-80000000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>3194000000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>339000000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>283000000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1513000000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1150000000</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>140000000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1010000000</v>
+      </c>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="n">
+        <v>1010000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B6" t="n">
+        <v>485221084</v>
+      </c>
+      <c r="C6" t="n">
+        <v>485221084</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2536000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-224000000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1409000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-759000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-224000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1613000000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>486000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1208000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>485000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>486000000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-919000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1240000000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1240000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>9703000000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2287000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>298000000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>3000000</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>54000000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>3111000000</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>-158000000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>3269000000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>179000000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>234000000</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1325000000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1858000000</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>276000000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1582000000</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1531000000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>1582000000</v>
+      <c r="Z6" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1875000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1153000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>722000000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>77000000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>7416000000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>74000000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>661000000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>460000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>201000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>140000000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>5955000000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>242000000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5713000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>10188000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>3531000000</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>364000000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>264000000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>710000000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>201000000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>509000000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2092000000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-2358000000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4450000000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2902000000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1504000000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>6657000000</v>
+      </c>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>3210000000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-65000000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>3275000000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>392000000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1511000000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1326000000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1208000000</v>
+      </c>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="n">
+        <v>1208000000</v>
       </c>
     </row>
   </sheetData>
@@ -2519,7 +2694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO5"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2726,476 +2901,527 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45565</v>
-      </c>
-      <c r="B2" t="n">
-        <v>645000000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>-763000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>847000000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-193000000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1010000000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>71000000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>897000000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-49000000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>91000000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-585000000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-17000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-209000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-5000000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>113000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>29000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>84000000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-763000000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>847000000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-162000000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>52000000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-59000000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>-59000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-193000000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-193000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>838000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-28000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>190000000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>662000000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>662000000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-21000000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>254000000</v>
-      </c>
+        <v>44469</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>153000000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45199</v>
+        <v>44834</v>
       </c>
       <c r="B3" t="n">
-        <v>828000000</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>-79000000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
       <c r="D3" t="n">
-        <v>-253000000</v>
+        <v>-514000000</v>
       </c>
       <c r="E3" t="n">
-        <v>248000000</v>
+        <v>415000000</v>
       </c>
       <c r="F3" t="n">
-        <v>-176000000</v>
+        <v>-206000000</v>
       </c>
       <c r="G3" t="n">
-        <v>897000000</v>
+        <v>769000000</v>
       </c>
       <c r="H3" t="n">
         <v>48000000</v>
       </c>
       <c r="I3" t="n">
-        <v>769000000</v>
+        <v>1582000000</v>
       </c>
       <c r="J3" t="n">
-        <v>-39000000</v>
+        <v>-21000000</v>
       </c>
       <c r="K3" t="n">
-        <v>119000000</v>
+        <v>-840000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-649000000</v>
+        <v>-932000000</v>
       </c>
       <c r="M3" t="n">
-        <v>-11000000</v>
+        <v>-169000000</v>
       </c>
       <c r="N3" t="n">
-        <v>-138000000</v>
+        <v>-74000000</v>
       </c>
       <c r="O3" t="n">
-        <v>-3000000</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+        <v>-104000000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
       <c r="R3" t="n">
-        <v>-8000000</v>
+        <v>-89000000</v>
       </c>
       <c r="S3" t="n">
-        <v>-3000000</v>
+        <v>10000000</v>
       </c>
       <c r="T3" t="n">
-        <v>-5000000</v>
+        <v>-99000000</v>
       </c>
       <c r="U3" t="n">
-        <v>-253000000</v>
+        <v>-514000000</v>
       </c>
       <c r="V3" t="n">
-        <v>248000000</v>
+        <v>415000000</v>
       </c>
       <c r="W3" t="n">
-        <v>-236000000</v>
+        <v>-35000000</v>
       </c>
       <c r="X3" t="n">
-        <v>30000000</v>
+        <v>53000000</v>
       </c>
       <c r="Y3" t="n">
-        <v>48000000</v>
+        <v>17000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-81000000</v>
+        <v>102000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>150000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-81000000</v>
+        <v>-48000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-57000000</v>
+        <v>-1000000</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-57000000</v>
+        <v>-1000000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-176000000</v>
+        <v>-206000000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-176000000</v>
+        <v>-206000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1004000000</v>
+        <v>127000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-109000000</v>
+        <v>-130000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>332000000</v>
+        <v>-381000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>835000000</v>
+        <v>761000000</v>
       </c>
       <c r="AL3" t="n">
-        <v>835000000</v>
+        <v>761000000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-17000000</v>
+        <v>-36000000</v>
       </c>
       <c r="AN3" t="n">
         <v>2000000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-21000000</v>
+        <v>105000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44834</v>
+        <v>45199</v>
       </c>
       <c r="B4" t="n">
-        <v>-79000000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
+        <v>828000000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-514000000</v>
+        <v>-253000000</v>
       </c>
       <c r="E4" t="n">
-        <v>415000000</v>
+        <v>248000000</v>
       </c>
       <c r="F4" t="n">
-        <v>-206000000</v>
+        <v>-176000000</v>
       </c>
       <c r="G4" t="n">
-        <v>769000000</v>
+        <v>897000000</v>
       </c>
       <c r="H4" t="n">
         <v>48000000</v>
       </c>
       <c r="I4" t="n">
-        <v>1582000000</v>
+        <v>769000000</v>
       </c>
       <c r="J4" t="n">
-        <v>-21000000</v>
+        <v>-39000000</v>
       </c>
       <c r="K4" t="n">
-        <v>-840000000</v>
+        <v>119000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-932000000</v>
+        <v>-649000000</v>
       </c>
       <c r="M4" t="n">
-        <v>-169000000</v>
+        <v>-11000000</v>
       </c>
       <c r="N4" t="n">
-        <v>-74000000</v>
+        <v>-138000000</v>
       </c>
       <c r="O4" t="n">
-        <v>-104000000</v>
-      </c>
-      <c r="P4" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>-8000000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-5000000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-253000000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>248000000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-236000000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-81000000</v>
+      </c>
+      <c r="AA4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-89000000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-99000000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-514000000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>415000000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-35000000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>53000000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>102000000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>150000000</v>
-      </c>
       <c r="AB4" t="n">
-        <v>-48000000</v>
+        <v>-81000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1000000</v>
+        <v>-57000000</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-1000000</v>
+        <v>-57000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-206000000</v>
+        <v>-176000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-206000000</v>
+        <v>-176000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>127000000</v>
+        <v>1004000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-130000000</v>
+        <v>-109000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-381000000</v>
+        <v>332000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>761000000</v>
+        <v>835000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>761000000</v>
+        <v>835000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-36000000</v>
+        <v>-17000000</v>
       </c>
       <c r="AN4" t="n">
         <v>2000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>105000000</v>
+        <v>-21000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44469</v>
+        <v>45565</v>
       </c>
       <c r="B5" t="n">
-        <v>309000000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
+        <v>645000000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-295000000</v>
+        <v>-763000000</v>
       </c>
       <c r="E5" t="n">
-        <v>781000000</v>
+        <v>847000000</v>
       </c>
       <c r="F5" t="n">
-        <v>-141000000</v>
+        <v>-193000000</v>
       </c>
       <c r="G5" t="n">
-        <v>1582000000</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>1010000000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>71000000</v>
+      </c>
       <c r="I5" t="n">
-        <v>1484000000</v>
+        <v>897000000</v>
       </c>
       <c r="J5" t="n">
-        <v>-12000000</v>
+        <v>-49000000</v>
       </c>
       <c r="K5" t="n">
-        <v>110000000</v>
+        <v>91000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-77000000</v>
+        <v>-585000000</v>
       </c>
       <c r="M5" t="n">
-        <v>23000000</v>
+        <v>-17000000</v>
       </c>
       <c r="N5" t="n">
-        <v>-62000000</v>
+        <v>-209000000</v>
       </c>
       <c r="O5" t="n">
-        <v>-21000000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
+        <v>-5000000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>486000000</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
+        <v>113000000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>29000000</v>
+      </c>
       <c r="T5" t="n">
-        <v>486000000</v>
+        <v>84000000</v>
       </c>
       <c r="U5" t="n">
-        <v>-295000000</v>
+        <v>-763000000</v>
       </c>
       <c r="V5" t="n">
-        <v>781000000</v>
+        <v>847000000</v>
       </c>
       <c r="W5" t="n">
-        <v>-263000000</v>
+        <v>-162000000</v>
       </c>
       <c r="X5" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+        <v>38000000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>52000000</v>
+      </c>
       <c r="Z5" t="n">
-        <v>-141000000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>153000000</v>
-      </c>
+        <v>-59000000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-294000000</v>
+        <v>-59000000</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-141000000</v>
+        <v>-193000000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-141000000</v>
+        <v>-193000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>450000000</v>
+        <v>838000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-104000000</v>
+        <v>-28000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-354000000</v>
+        <v>190000000</v>
       </c>
       <c r="AK5" t="n">
-        <v>621000000</v>
+        <v>662000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>621000000</v>
+        <v>662000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-48000000</v>
+        <v>-21000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="AO5" t="n">
-        <v>326000000</v>
+        <v>254000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B6" t="n">
+        <v>860000000</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>-90000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-190000000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1207000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1010000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-71000000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-687000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-12000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-218000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-7000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-90000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-155000000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-59000000</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>-59000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-190000000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-190000000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>701000000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>701000000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-41000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>241000000</v>
       </c>
     </row>
   </sheetData>
@@ -3209,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EG2"/>
+  <dimension ref="A1:EF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3360,540 +3586,535 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>trailingPE</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
       <c r="EF1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3910,10 +4131,8 @@
           <t>Düsseldorf</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>40221</t>
-        </is>
+      <c r="C2" t="n">
+        <v>40221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3988,7 +4207,7 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>4.01</v>
+        <v>3.745</v>
       </c>
       <c r="U2" t="n">
         <v>4.01</v>
@@ -4000,7 +4219,7 @@
         <v>4.01</v>
       </c>
       <c r="X2" t="n">
-        <v>4.01</v>
+        <v>3.745</v>
       </c>
       <c r="Y2" t="n">
         <v>4.01</v>
@@ -4015,372 +4234,369 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.685</v>
+        <v>1.684</v>
       </c>
       <c r="AD2" t="n">
-        <v>404</v>
+        <v>3296</v>
       </c>
       <c r="AE2" t="n">
         <v>3296</v>
       </c>
       <c r="AF2" t="n">
-        <v>3296</v>
+        <v>166</v>
       </c>
       <c r="AG2" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>791</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>791</v>
+        <v>3.685</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4.01</v>
+        <v>3.795</v>
       </c>
       <c r="AK2" t="n">
-        <v>4.06</v>
+        <v>1824431232</v>
       </c>
       <c r="AL2" t="n">
-        <v>1960293120</v>
+        <v>1824431275</v>
       </c>
       <c r="AM2" t="n">
-        <v>1940884336</v>
+        <v>2.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.805</v>
+        <v>4.575</v>
       </c>
       <c r="AO2" t="n">
         <v>4.575</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.575</v>
+        <v>1.774</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.774</v>
+        <v>0.07822455</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.08404978</v>
+        <v>4.1522</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2419</v>
+        <v>4.333325</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.361275</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AW2" t="b">
         <v>0</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="n">
+        <v>3407300864</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.00257</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>176135253</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>485221084</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.72762</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>485221084</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.7934623</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1759190400</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1790726400</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-60000000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>6.954</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0.38275862</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BQ2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BS2" t="n">
+        <v>1096999936</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>2.261</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>490000000</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>2692999936</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>23323000832</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>413.037</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>48.067</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.019170001</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>-0.091759995</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>4243000064</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>670774976</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>1036000000</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.18191999</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.02101</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="CK2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="AX2" t="b">
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>1CEC.MI</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="CQ2" t="b">
         <v>0</v>
       </c>
-      <c r="AY2" t="n">
-        <v>3555293184</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-0.00257</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>176135253</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>485221084</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.72762</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.15483</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>485221084</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.346</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.001486</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1759190400</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1790726400</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1774915200</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>-60000000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>7.256</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.42959</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="BR2" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="BT2" t="n">
-        <v>1096999936</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>2.261</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>490000000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>2692999936</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.928</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>23323000832</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>413.037</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>48.067</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>0.019170001</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>-0.091759995</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>4243000064</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>670774976</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>1036000000</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0.18191999</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>0.02101</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>-0.0011</v>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>1CEC.MI</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="CR2" t="b">
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CT2" t="n">
+        <v>1780313441</v>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>finmb_875173</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="CY2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="DA2" t="b">
         <v>0</v>
       </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="CU2" t="n">
-        <v>-0.07366543</v>
-      </c>
-      <c r="CV2" t="n">
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>CECONOMY</t>
+        </is>
+      </c>
+      <c r="DC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>1702368000000</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.015000105</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>4.01 - 4.01</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>166</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.8599999</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.29655167</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>2.9 - 4.575</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.8149998000000001</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.17814204</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>38.275864</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1785425400</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1785425400</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1785425400</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1778659200</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1778659200</v>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.39220023</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.094456</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.5733249</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.13230601</v>
+      </c>
+      <c r="DZ2" t="n">
         <v>20</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="EA2" t="n">
         <v>15</v>
       </c>
-      <c r="CX2" t="b">
+      <c r="EB2" t="b">
         <v>0</v>
       </c>
-      <c r="CY2" t="n">
-        <v>0.748123</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>1780313441</v>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>finmb_875173</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="DI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0.029999733</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>4.01 - 4.01</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>169</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>1.2349999</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.44028515</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>2.805 - 4.575</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.5349998500000001</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.116939865</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>42.959</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1785425400</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1785425400</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1785425400</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1778659200</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1778659200</v>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.2019</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.047596596</v>
-      </c>
       <c r="EC2" t="n">
-        <v>-0.32127523</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>CECONOMY</t>
-        </is>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1702368000000</v>
-      </c>
-      <c r="EG2" t="inlineStr"/>
+        <v>0.4005369</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
